--- a/hardware/fabrication/BOM_MOAR_MOAR_Board_2025-09-02.xlsx
+++ b/hardware/fabrication/BOM_MOAR_MOAR_Board_2025-09-02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="278">
   <si>
     <t>No.</t>
   </si>
@@ -73,13 +73,217 @@
     <t>1</t>
   </si>
   <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.4-FD</t>
+  </si>
+  <si>
+    <t>RVT1E221M0607</t>
+  </si>
+  <si>
+    <t>ROQANG(容强)</t>
+  </si>
+  <si>
+    <t>C2918361</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>266097</t>
+  </si>
+  <si>
+    <t>0.0043</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C1206</t>
+  </si>
+  <si>
+    <t>HGC1206R5107M100NSPJ</t>
+  </si>
+  <si>
+    <t>Chinocera(华瓷)</t>
+  </si>
+  <si>
+    <t>C7432784</t>
+  </si>
+  <si>
+    <t>Capacitors</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
+  </si>
+  <si>
+    <t>135330</t>
+  </si>
+  <si>
+    <t>0.0195</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C0805</t>
+  </si>
+  <si>
+    <t>CGA0805X7R475K350MT</t>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+  </si>
+  <si>
+    <t>C6119943</t>
+  </si>
+  <si>
+    <t>724153</t>
+  </si>
+  <si>
+    <t>0.0038</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C4,C17,C71,C72,C74,C75,C76,C77,C81,C82,C83,C84,C88,C89</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C15849</t>
+  </si>
+  <si>
+    <t>10897932</t>
+  </si>
+  <si>
+    <t>0.0007</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>CL10A106MA8NRNC</t>
+  </si>
+  <si>
+    <t>C96446</t>
+  </si>
+  <si>
+    <t>3062628</t>
+  </si>
+  <si>
+    <t>0.0026</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R9BB472</t>
+  </si>
+  <si>
+    <t>YAGEO(国巨)</t>
+  </si>
+  <si>
+    <t>C106208</t>
+  </si>
+  <si>
+    <t>137388</t>
+  </si>
+  <si>
+    <t>0.0002</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1000uF</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
+  </si>
+  <si>
+    <t>NPXD0901B102MJTM</t>
+  </si>
+  <si>
+    <t>Ymin(永铭)</t>
+  </si>
+  <si>
+    <t>C2976189</t>
+  </si>
+  <si>
+    <t>Aluminum Electrolytic Capacitors - Leaded</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.0422</t>
+  </si>
+  <si>
+    <t>DIP</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>100nF</t>
   </si>
   <si>
-    <t>C2,C4,C6,C9,C10,C25,C37,C47,C50,C61,C62,C63,C78,C79,C80,C81,C82,C83,C85,C86,C87,C88,C89,C90,C91,C92,C93,C94,C95,C96,C97,C98,C99,C100,C101,C102,C103,C104,C105,C106,C107,C108,C109,C110,C111,C112,C113,C114,C114,C115,C116,C117,C118,C119,C120,C122,C123,C124,C125,C126,C127,C128,C135</t>
-  </si>
-  <si>
-    <t>C0603</t>
+    <t>C21,C22,C23,C24,C25,C27,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43,C44,C45,C46,C47,C48,C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62,C63,C64,C65,C66,C67,C68,C69,C70,C73,C78,C79,C80,C81,C82,C83,C85,C85,C86,C87,C88,C89,C90,C91,C135</t>
   </si>
   <si>
     <t>TCC0603X7R104K500CT</t>
@@ -91,216 +295,12 @@
     <t>C282519</t>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>14723365</t>
+    <t>14723065</t>
   </si>
   <si>
     <t>0.0003</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.4-FD</t>
-  </si>
-  <si>
-    <t>RVT1E221M0607</t>
-  </si>
-  <si>
-    <t>ROQANG(容强)</t>
-  </si>
-  <si>
-    <t>C2918361</t>
-  </si>
-  <si>
-    <t>266249</t>
-  </si>
-  <si>
-    <t>0.0043</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C1206</t>
-  </si>
-  <si>
-    <t>HGC1206R5107M100NSPJ</t>
-  </si>
-  <si>
-    <t>Chinocera(华瓷)</t>
-  </si>
-  <si>
-    <t>C7432784</t>
-  </si>
-  <si>
-    <t>Capacitors</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
-  </si>
-  <si>
-    <t>135146</t>
-  </si>
-  <si>
-    <t>0.0195</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C8,C11,C12,C39,C40,C42,C43,C45,C46,C48,C49,C51,C52,C54</t>
-  </si>
-  <si>
-    <t>CL10A105KB8NNNC</t>
-  </si>
-  <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>C15849</t>
-  </si>
-  <si>
-    <t>10921386</t>
-  </si>
-  <si>
-    <t>0.0007</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>C0805</t>
-  </si>
-  <si>
-    <t>CGA0805X7R475K350MT</t>
-  </si>
-  <si>
-    <t>HRE(芯声)</t>
-  </si>
-  <si>
-    <t>C6119943</t>
-  </si>
-  <si>
-    <t>724193</t>
-  </si>
-  <si>
-    <t>0.0038</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C56</t>
-  </si>
-  <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
-    <t>C96446</t>
-  </si>
-  <si>
-    <t>3076444</t>
-  </si>
-  <si>
-    <t>0.0026</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>4.7nF</t>
-  </si>
-  <si>
-    <t>C60</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>CC0402KRX7R9BB472</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>C106208</t>
-  </si>
-  <si>
-    <t>137428</t>
-  </si>
-  <si>
-    <t>0.0002</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1000uF</t>
-  </si>
-  <si>
-    <t>C121</t>
-  </si>
-  <si>
-    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
-  </si>
-  <si>
-    <t>NPXD0901B102MJTM</t>
-  </si>
-  <si>
-    <t>Ymin(永铭)</t>
-  </si>
-  <si>
-    <t>C2976189</t>
-  </si>
-  <si>
-    <t>Aluminum Electrolytic Capacitors - Leaded</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.0422</t>
-  </si>
-  <si>
-    <t>DIP</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -445,7 +445,7 @@
     <t>C431533</t>
   </si>
   <si>
-    <t>35812</t>
+    <t>35776</t>
   </si>
   <si>
     <t>0.0071</t>
@@ -469,7 +469,7 @@
     <t>C2939346</t>
   </si>
   <si>
-    <t>967</t>
+    <t>852</t>
   </si>
   <si>
     <t>0.0468</t>
@@ -511,7 +511,7 @@
     <t>C965804</t>
   </si>
   <si>
-    <t>668631</t>
+    <t>665091</t>
   </si>
   <si>
     <t>0.0006</t>
@@ -538,7 +538,7 @@
     <t>C17673</t>
   </si>
   <si>
-    <t>4933169</t>
+    <t>4926853</t>
   </si>
   <si>
     <t>19</t>
@@ -556,7 +556,7 @@
     <t>C17557</t>
   </si>
   <si>
-    <t>742357</t>
+    <t>742417</t>
   </si>
   <si>
     <t>20</t>
@@ -574,7 +574,7 @@
     <t>C17630</t>
   </si>
   <si>
-    <t>1015647</t>
+    <t>1012115</t>
   </si>
   <si>
     <t>21</t>
@@ -592,7 +592,7 @@
     <t>C149504</t>
   </si>
   <si>
-    <t>1990995</t>
+    <t>1988010</t>
   </si>
   <si>
     <t>22</t>
@@ -610,7 +610,7 @@
     <t>C25612</t>
   </si>
   <si>
-    <t>763023</t>
+    <t>762923</t>
   </si>
   <si>
     <t>23</t>
@@ -628,7 +628,7 @@
     <t>C4328</t>
   </si>
   <si>
-    <t>1247796</t>
+    <t>1251010</t>
   </si>
   <si>
     <t>RV1,RV2,RV3</t>
@@ -646,7 +646,7 @@
     <t>C209779</t>
   </si>
   <si>
-    <t>5064</t>
+    <t>5031</t>
   </si>
   <si>
     <t>0.1108</t>
@@ -748,7 +748,10 @@
     <t>33</t>
   </si>
   <si>
-    <t>23.4941</t>
+    <t>60</t>
+  </si>
+  <si>
+    <t>0.4044</t>
   </si>
   <si>
     <t>29</t>
@@ -790,7 +793,7 @@
     <t>7107</t>
   </si>
   <si>
-    <t>0.2124</t>
+    <t>0.1987</t>
   </si>
   <si>
     <t>31</t>
@@ -838,7 +841,7 @@
     <t>C5145244</t>
   </si>
   <si>
-    <t>16327</t>
+    <t>16325</t>
   </si>
   <si>
     <t>0.0164</t>
@@ -1288,7 +1291,7 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -1374,10 +1377,10 @@
         <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
@@ -1389,10 +1392,10 @@
         <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R3" t="s">
         <v>31</v>
@@ -1403,40 +1406,40 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
         <v>44</v>
       </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
         <v>28</v>
@@ -1474,19 +1477,19 @@
         <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
@@ -1507,10 +1510,10 @@
         <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R5" t="s">
         <v>31</v>
@@ -1521,31 +1524,31 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
         <v>62</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>64</v>
       </c>
       <c r="H6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
         <v>65</v>
-      </c>
-      <c r="I6" t="s">
-        <v>66</v>
       </c>
       <c r="J6" t="s">
         <v>26</v>
@@ -1566,10 +1569,10 @@
         <v>27</v>
       </c>
       <c r="P6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6" t="s">
         <v>67</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>68</v>
       </c>
       <c r="R6" t="s">
         <v>31</v>
@@ -1580,31 +1583,31 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>71</v>
       </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
         <v>72</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -1625,10 +1628,10 @@
         <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R7" t="s">
         <v>31</v>
@@ -1639,40 +1642,40 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
         <v>78</v>
       </c>
-      <c r="E8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" t="s">
-        <v>77</v>
-      </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s">
         <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s">
         <v>28</v>
@@ -1684,54 +1687,54 @@
         <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R8" t="s">
         <v>31</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="M9" t="s">
         <v>28</v>
@@ -1743,16 +1746,16 @@
         <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" t="s">
         <v>31</v>
       </c>
       <c r="S9" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1929,7 +1932,7 @@
         <v>31</v>
       </c>
       <c r="S12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1979,7 +1982,7 @@
         <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q13" t="s">
         <v>129</v>
@@ -1988,7 +1991,7 @@
         <v>31</v>
       </c>
       <c r="S13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2088,7 +2091,7 @@
         <v>27</v>
       </c>
       <c r="M15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N15" t="s">
         <v>27</v>
@@ -2106,7 +2109,7 @@
         <v>31</v>
       </c>
       <c r="S15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2147,7 +2150,7 @@
         <v>27</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
@@ -2165,7 +2168,7 @@
         <v>31</v>
       </c>
       <c r="S16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -2224,7 +2227,7 @@
         <v>31</v>
       </c>
       <c r="S17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -2336,7 +2339,7 @@
         <v>175</v>
       </c>
       <c r="Q19" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R19" t="s">
         <v>31</v>
@@ -2395,7 +2398,7 @@
         <v>181</v>
       </c>
       <c r="Q20" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R20" t="s">
         <v>31</v>
@@ -2454,7 +2457,7 @@
         <v>187</v>
       </c>
       <c r="Q21" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R21" t="s">
         <v>31</v>
@@ -2513,7 +2516,7 @@
         <v>193</v>
       </c>
       <c r="Q22" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R22" t="s">
         <v>31</v>
@@ -2572,7 +2575,7 @@
         <v>199</v>
       </c>
       <c r="Q23" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R23" t="s">
         <v>31</v>
@@ -2631,7 +2634,7 @@
         <v>205</v>
       </c>
       <c r="Q24" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="R24" t="s">
         <v>31</v>
@@ -2678,7 +2681,7 @@
         <v>27</v>
       </c>
       <c r="M25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N25" t="s">
         <v>27</v>
@@ -2696,7 +2699,7 @@
         <v>31</v>
       </c>
       <c r="S25" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -2755,7 +2758,7 @@
         <v>31</v>
       </c>
       <c r="S26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -2855,7 +2858,7 @@
         <v>236</v>
       </c>
       <c r="M28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N28" t="s">
         <v>27</v>
@@ -2873,7 +2876,7 @@
         <v>31</v>
       </c>
       <c r="S28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -2917,10 +2920,10 @@
         <v>244</v>
       </c>
       <c r="N29" t="s">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="O29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P29" t="s">
         <v>27</v>
@@ -2932,36 +2935,36 @@
         <v>31</v>
       </c>
       <c r="S29" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" t="s">
+        <v>250</v>
+      </c>
+      <c r="F30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" t="s">
         <v>248</v>
       </c>
-      <c r="E30" t="s">
-        <v>249</v>
-      </c>
-      <c r="F30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" t="s">
-        <v>247</v>
-      </c>
       <c r="H30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J30" t="s">
         <v>26</v>
@@ -2973,54 +2976,54 @@
         <v>27</v>
       </c>
       <c r="M30" t="s">
+        <v>88</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" t="s">
         <v>85</v>
       </c>
-      <c r="N30" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" t="s">
-        <v>93</v>
-      </c>
       <c r="Q30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R30" t="s">
         <v>31</v>
       </c>
       <c r="S30" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s">
+        <v>256</v>
+      </c>
+      <c r="E31" t="s">
+        <v>257</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" t="s">
         <v>255</v>
-      </c>
-      <c r="E31" t="s">
-        <v>256</v>
-      </c>
-      <c r="F31" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" t="s">
-        <v>254</v>
       </c>
       <c r="H31" t="s">
         <v>125</v>
       </c>
       <c r="I31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J31" t="s">
         <v>26</v>
@@ -3041,10 +3044,10 @@
         <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R31" t="s">
         <v>31</v>
@@ -3055,40 +3058,40 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" t="s">
+        <v>264</v>
+      </c>
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" t="s">
         <v>262</v>
-      </c>
-      <c r="E32" t="s">
-        <v>263</v>
-      </c>
-      <c r="F32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" t="s">
-        <v>261</v>
       </c>
       <c r="H32" t="s">
         <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J32" t="s">
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s">
         <v>138</v>
@@ -3100,45 +3103,45 @@
         <v>27</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R32" t="s">
         <v>31</v>
       </c>
       <c r="S32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E33" t="s">
+        <v>273</v>
+      </c>
+      <c r="F33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" t="s">
         <v>271</v>
       </c>
-      <c r="E33" t="s">
-        <v>272</v>
-      </c>
-      <c r="F33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" t="s">
-        <v>270</v>
-      </c>
       <c r="H33" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J33" t="s">
         <v>26</v>
@@ -3150,7 +3153,7 @@
         <v>27</v>
       </c>
       <c r="M33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N33" t="s">
         <v>27</v>
@@ -3159,10 +3162,10 @@
         <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R33" t="s">
         <v>31</v>
